--- a/LSOL_MASTER_QA.xlsx
+++ b/LSOL_MASTER_QA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30114"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal folders\Programmation\Games\gtav_industry_mgnt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10060CC2-3E16-4FD9-A7E5-EE8BB1400EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC732446-F306-43F7-B529-691EC049D69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00B1FBEB-483D-48F3-9154-6B5AEE763F1C}"/>
   </bookViews>
@@ -7994,653 +7994,653 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="40" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="1">
         <v>2</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K40" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L40" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M40" t="s">
+      <c r="M40" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N40" t="s">
+      <c r="N40" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O40" t="s">
+      <c r="O40" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P40" t="s">
+      <c r="P40" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="Q40" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R40" t="s">
+      <c r="R40" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S40" t="s">
+      <c r="S40" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U40" t="s">
+      <c r="U40" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V40" t="s">
+      <c r="V40" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="41" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="1">
         <v>2</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="1" t="s">
         <v>1449</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K41" t="s">
+      <c r="K41" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L41" t="s">
+      <c r="L41" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M41" t="s">
+      <c r="M41" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N41" t="s">
+      <c r="N41" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O41" t="s">
+      <c r="O41" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P41" t="s">
+      <c r="P41" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="Q41" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R41" t="s">
+      <c r="R41" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S41" t="s">
+      <c r="S41" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U41" t="s">
+      <c r="U41" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V41" t="s">
+      <c r="V41" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="42" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="1">
         <v>2</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K42" t="s">
+      <c r="K42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L42" t="s">
+      <c r="L42" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M42" t="s">
+      <c r="M42" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N42" t="s">
+      <c r="N42" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O42" t="s">
+      <c r="O42" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P42" t="s">
+      <c r="P42" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="Q42" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R42" t="s">
+      <c r="R42" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S42" t="s">
+      <c r="S42" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U42" t="s">
+      <c r="U42" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V42" t="s">
+      <c r="V42" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="43" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="1">
         <v>2</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K43" t="s">
+      <c r="K43" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L43" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M43" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N43" t="s">
+      <c r="N43" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O43" t="s">
+      <c r="O43" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P43" t="s">
+      <c r="P43" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="Q43" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R43" t="s">
+      <c r="R43" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S43" t="s">
+      <c r="S43" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U43" t="s">
+      <c r="U43" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V43" t="s">
+      <c r="V43" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="44" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="1">
         <v>2</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="1" t="s">
         <v>1452</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K44" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L44" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M44" t="s">
+      <c r="M44" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N44" t="s">
+      <c r="N44" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O44" t="s">
+      <c r="O44" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P44" t="s">
+      <c r="P44" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="Q44" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R44" t="s">
+      <c r="R44" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S44" t="s">
+      <c r="S44" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U44" t="s">
+      <c r="U44" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V44" t="s">
+      <c r="V44" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="45" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="1">
         <v>2</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="1" t="s">
         <v>1453</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K45" t="s">
+      <c r="K45" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L45" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M45" t="s">
+      <c r="M45" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N45" t="s">
+      <c r="N45" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O45" t="s">
+      <c r="O45" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P45" t="s">
+      <c r="P45" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="Q45" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R45" t="s">
+      <c r="R45" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S45" t="s">
+      <c r="S45" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U45" t="s">
+      <c r="U45" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V45" t="s">
+      <c r="V45" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="46" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="1">
         <v>2</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="1" t="s">
         <v>1454</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K46" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L46" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M46" t="s">
+      <c r="M46" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N46" t="s">
+      <c r="N46" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O46" t="s">
+      <c r="O46" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P46" t="s">
+      <c r="P46" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="Q46" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R46" t="s">
+      <c r="R46" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S46" t="s">
+      <c r="S46" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U46" t="s">
+      <c r="U46" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V46" t="s">
+      <c r="V46" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="47" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="1">
         <v>2</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="1" t="s">
         <v>1455</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K47" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M47" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N47" t="s">
+      <c r="N47" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O47" t="s">
+      <c r="O47" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P47" t="s">
+      <c r="P47" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="Q47" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R47" t="s">
+      <c r="R47" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S47" t="s">
+      <c r="S47" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U47" t="s">
+      <c r="U47" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V47" t="s">
+      <c r="V47" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="48" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="1">
         <v>2</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="1" t="s">
         <v>1456</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K48" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L48" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M48" t="s">
+      <c r="M48" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N48" t="s">
+      <c r="N48" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O48" t="s">
+      <c r="O48" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P48" t="s">
+      <c r="P48" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="Q48" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R48" t="s">
+      <c r="R48" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S48" t="s">
+      <c r="S48" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U48" t="s">
+      <c r="U48" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V48" t="s">
+      <c r="V48" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="49" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="1">
         <v>2</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>1513</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K49" t="s">
+      <c r="K49" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L49" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M49" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="N49" t="s">
+      <c r="N49" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="O49" t="s">
+      <c r="O49" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="P49" t="s">
+      <c r="P49" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="Q49" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="R49" t="s">
+      <c r="R49" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="S49" t="s">
+      <c r="S49" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="U49" t="s">
+      <c r="U49" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="V49" t="s">
+      <c r="V49" s="1" t="s">
         <v>41</v>
       </c>
     </row>
